--- a/Projects/MISQ/MISQ round 2/writeup/explore260606_new 3 IV plot.xlsx
+++ b/Projects/MISQ/MISQ round 2/writeup/explore260606_new 3 IV plot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/writeup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AB4AEA-EDCD-CD4D-B998-D8C4694F227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606A5682-B69E-2B4E-88C8-5D787AA3CA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19540" activeTab="1" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19540" activeTab="2" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1756,7 +1756,16 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1765,20 +1774,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3135,9 +3135,11 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
+              <a:headEnd type="oval"/>
+              <a:tailEnd type="oval"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -3146,15 +3148,18 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'interaction plot'!$A$45:$A$46</c:f>
+              <c:f>'interaction plot'!$A$45:$A$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0.25836000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.63216220000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3198,9 +3203,14 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
+              <a:headEnd type="oval"/>
+              <a:tailEnd type="oval"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -3261,7 +3271,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="t"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -3375,7 +3385,7 @@
       <c:valAx>
         <c:axId val="1273565424"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -10582,6 +10592,54 @@
     <row r="90" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="B78:B89"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="B56:B67"/>
+    <mergeCell ref="B69:B76"/>
+    <mergeCell ref="B25:B32"/>
     <mergeCell ref="C65:C66"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
@@ -10598,54 +10656,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B22"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="B56:B67"/>
-    <mergeCell ref="B69:B76"/>
-    <mergeCell ref="B25:B32"/>
-    <mergeCell ref="B78:B89"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C39:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11523,35 +11533,35 @@
       <c r="B3" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31" t="s">
+      <c r="D3" s="38"/>
+      <c r="E3" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="31"/>
+      <c r="F3" s="38"/>
       <c r="H3" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31" t="s">
+      <c r="J3" s="38"/>
+      <c r="K3" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="31"/>
+      <c r="L3" s="38"/>
       <c r="N3" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="P3" s="31"/>
+      <c r="P3" s="38"/>
     </row>
     <row r="4" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="35" t="s">
         <v>334</v>
       </c>
       <c r="C4" s="14" t="s">
@@ -11566,7 +11576,7 @@
       <c r="F4" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="35" t="s">
         <v>334</v>
       </c>
       <c r="I4" s="14" t="s">
@@ -11581,7 +11591,7 @@
       <c r="L4" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="35" t="s">
         <v>334</v>
       </c>
       <c r="O4" s="14" t="s">
@@ -11592,7 +11602,7 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="32"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
@@ -11605,7 +11615,7 @@
       <c r="F5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="32"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="14" t="s">
         <v>29</v>
       </c>
@@ -11618,7 +11628,7 @@
       <c r="L5" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="N5" s="32"/>
+      <c r="N5" s="35"/>
       <c r="O5" s="14" t="s">
         <v>65</v>
       </c>
@@ -11627,7 +11637,7 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="35" t="s">
         <v>364</v>
       </c>
       <c r="C6" s="14"/>
@@ -11638,7 +11648,7 @@
       <c r="F6" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="35" t="s">
         <v>360</v>
       </c>
       <c r="J6" s="14" t="s">
@@ -11648,7 +11658,7 @@
       <c r="L6" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="35" t="s">
         <v>360</v>
       </c>
       <c r="P6" s="14" t="s">
@@ -11656,7 +11666,7 @@
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="32"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14" t="s">
         <v>26</v>
@@ -11665,7 +11675,7 @@
       <c r="F7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="35"/>
       <c r="J7" s="14" t="s">
         <v>213</v>
       </c>
@@ -11673,13 +11683,13 @@
       <c r="L7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="32"/>
+      <c r="N7" s="35"/>
       <c r="P7" s="14" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="35" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="14"/>
@@ -11690,7 +11700,7 @@
       <c r="F8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="35" t="s">
         <v>361</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -11700,7 +11710,7 @@
       <c r="L8" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="N8" s="35" t="s">
         <v>361</v>
       </c>
       <c r="P8" s="14" t="s">
@@ -11708,7 +11718,7 @@
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="33"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17" t="s">
         <v>85</v>
@@ -11717,7 +11727,7 @@
       <c r="F9" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="35"/>
       <c r="J9" s="14" t="s">
         <v>163</v>
       </c>
@@ -11725,7 +11735,7 @@
       <c r="L9" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="32"/>
+      <c r="N9" s="35"/>
       <c r="P9" s="14" t="s">
         <v>217</v>
       </c>
@@ -11746,7 +11756,7 @@
       <c r="F10" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="35" t="s">
         <v>362</v>
       </c>
       <c r="I10" s="14"/>
@@ -11757,7 +11767,7 @@
       <c r="L10" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="N10" s="32" t="s">
+      <c r="N10" s="35" t="s">
         <v>362</v>
       </c>
       <c r="O10" s="14"/>
@@ -11781,7 +11791,7 @@
       <c r="F11" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="s">
         <v>251</v>
@@ -11790,7 +11800,7 @@
       <c r="L11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="32"/>
+      <c r="N11" s="35"/>
       <c r="O11" s="14"/>
       <c r="P11" s="14" t="s">
         <v>213</v>
@@ -11812,7 +11822,7 @@
       <c r="F12" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="35" t="s">
         <v>363</v>
       </c>
       <c r="I12" s="14"/>
@@ -11823,7 +11833,7 @@
       <c r="L12" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="32" t="s">
+      <c r="N12" s="35" t="s">
         <v>363</v>
       </c>
       <c r="O12" s="14"/>
@@ -11847,7 +11857,7 @@
       <c r="F13" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17" t="s">
         <v>210</v>
@@ -11856,7 +11866,7 @@
       <c r="L13" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="N13" s="33"/>
+      <c r="N13" s="36"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17" t="s">
         <v>60</v>
@@ -11984,23 +11994,23 @@
     </row>
     <row r="23" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36" t="s">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="37" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="35"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="20" t="s">
         <v>328</v>
       </c>
@@ -12010,11 +12020,11 @@
       <c r="E25" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="31" t="s">
         <v>331</v>
       </c>
       <c r="C26" s="18" t="str">
@@ -12029,17 +12039,17 @@
         <f>"89.272"</f>
         <v>89.272</v>
       </c>
-      <c r="F26" s="35" t="str">
+      <c r="F26" s="32" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G26" s="35" t="str">
+      <c r="G26" s="32" t="str">
         <f>"2702.000"</f>
         <v>2702.000</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="34"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="18" t="str">
         <f>"(113.981)"</f>
         <v>(113.981)</v>
@@ -12052,11 +12062,11 @@
         <f>"(133.323)"</f>
         <v>(133.323)</v>
       </c>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="31" t="s">
         <v>332</v>
       </c>
       <c r="C28" s="18" t="str">
@@ -12071,17 +12081,17 @@
         <f>"1.372"</f>
         <v>1.372</v>
       </c>
-      <c r="F28" s="35" t="str">
+      <c r="F28" s="32" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G28" s="35" t="str">
+      <c r="G28" s="32" t="str">
         <f>"8.000"</f>
         <v>8.000</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B29" s="34"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="18" t="str">
         <f>"(1.166)"</f>
         <v>(1.166)</v>
@@ -12094,11 +12104,11 @@
         <f>"(1.192)"</f>
         <v>(1.192)</v>
       </c>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="31" t="s">
         <v>355</v>
       </c>
       <c r="C30" s="18" t="str">
@@ -12113,17 +12123,17 @@
         <f>"0.397"</f>
         <v>0.397</v>
       </c>
-      <c r="F30" s="35" t="str">
+      <c r="F30" s="32" t="str">
         <f>"-0.048"</f>
         <v>-0.048</v>
       </c>
-      <c r="G30" s="35" t="str">
+      <c r="G30" s="32" t="str">
         <f>"0.991"</f>
         <v>0.991</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="34"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="18" t="str">
         <f>"(0.181)"</f>
         <v>(0.181)</v>
@@ -12136,11 +12146,11 @@
         <f>"(0.188)"</f>
         <v>(0.188)</v>
       </c>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="31" t="s">
         <v>333</v>
       </c>
       <c r="C32" s="18" t="str">
@@ -12155,17 +12165,17 @@
         <f>"0.536"</f>
         <v>0.536</v>
       </c>
-      <c r="F32" s="35" t="str">
+      <c r="F32" s="32" t="str">
         <f>"-3.000"</f>
         <v>-3.000</v>
       </c>
-      <c r="G32" s="35" t="str">
+      <c r="G32" s="32" t="str">
         <f>"14.000"</f>
         <v>14.000</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="34"/>
+      <c r="B33" s="31"/>
       <c r="C33" s="18" t="str">
         <f>"(1.096)"</f>
         <v>(1.096)</v>
@@ -12178,11 +12188,11 @@
         <f>"(1.140)"</f>
         <v>(1.140)</v>
       </c>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="31" t="s">
         <v>357</v>
       </c>
       <c r="C34" s="18" t="str">
@@ -12197,17 +12207,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F34" s="35" t="str">
+      <c r="F34" s="32" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G34" s="35" t="str">
+      <c r="G34" s="32" t="str">
         <f>"6.977"</f>
         <v>6.977</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="34"/>
+      <c r="B35" s="31"/>
       <c r="C35" s="18" t="str">
         <f>"(2.864)"</f>
         <v>(2.864)</v>
@@ -12220,11 +12230,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="31" t="s">
         <v>359</v>
       </c>
       <c r="C36" s="18" t="str">
@@ -12239,17 +12249,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F36" s="35" t="str">
+      <c r="F36" s="32" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G36" s="35" t="str">
+      <c r="G36" s="32" t="str">
         <f>"0.891"</f>
         <v>0.891</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="34"/>
+      <c r="B37" s="31"/>
       <c r="C37" s="18" t="str">
         <f>"(0.297)"</f>
         <v>(0.297)</v>
@@ -12262,11 +12272,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="31" t="s">
         <v>358</v>
       </c>
       <c r="C38" s="18" t="str">
@@ -12281,17 +12291,17 @@
         <f>"3.443"</f>
         <v>3.443</v>
       </c>
-      <c r="F38" s="35" t="str">
+      <c r="F38" s="32" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G38" s="35" t="str">
+      <c r="G38" s="32" t="str">
         <f>"7.912"</f>
         <v>7.912</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B39" s="34"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="18" t="str">
         <f>"(1.489)"</f>
         <v>(1.489)</v>
@@ -12304,11 +12314,11 @@
         <f>"(1.338)"</f>
         <v>(1.338)</v>
       </c>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="31" t="s">
         <v>356</v>
       </c>
       <c r="C40" s="18" t="str">
@@ -12323,17 +12333,17 @@
         <f>"0.445"</f>
         <v>0.445</v>
       </c>
-      <c r="F40" s="35" t="str">
+      <c r="F40" s="32" t="str">
         <f>"-0.090"</f>
         <v>-0.090</v>
       </c>
-      <c r="G40" s="35" t="str">
+      <c r="G40" s="32" t="str">
         <f>"0.911"</f>
         <v>0.911</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B41" s="38"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="19" t="str">
         <f>"(0.177)"</f>
         <v>(0.177)</v>
@@ -12346,29 +12356,25 @@
         <f>"(0.187)"</f>
         <v>(0.187)</v>
       </c>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="F28:F29"/>
     <mergeCell ref="G28:G29"/>
@@ -12383,20 +12389,24 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
